--- a/tams-invest-parent/tams-invest-basicdata/src/main/resources/tpl/MstSharePrice.xlsx
+++ b/tams-invest-parent/tams-invest-basicdata/src/main/resources/tpl/MstSharePrice.xlsx
@@ -1,7 +1,7 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="5" lowestEdited="4" rupBuild="9302"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="4" rupBuild="14420"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
   <bookViews>
     <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010"/>
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="23">
   <si>
     <t>资产代码</t>
   </si>
@@ -92,6 +92,10 @@
   </si>
   <si>
     <t>交易状态</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>币种</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -147,12 +151,15 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
     </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
   </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 主题​​">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 主题">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -194,7 +201,7 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria"/>
+        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -229,7 +236,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri"/>
+        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -438,24 +445,24 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:V1"/>
+  <dimension ref="A1:W1"/>
   <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="3" max="3" width="12.875" customWidth="1"/>
     <col min="4" max="4" width="12.625" customWidth="1"/>
-    <col min="5" max="5" width="13.625" customWidth="1"/>
-    <col min="6" max="6" width="13.125" customWidth="1"/>
-    <col min="7" max="7" width="10.25" customWidth="1"/>
-    <col min="8" max="8" width="10.125" customWidth="1"/>
-    <col min="9" max="9" width="13.625" customWidth="1"/>
-    <col min="16" max="16" width="14.5" customWidth="1"/>
-    <col min="17" max="17" width="14.875" customWidth="1"/>
-    <col min="18" max="18" width="15.75" customWidth="1"/>
-    <col min="19" max="19" width="14.5" customWidth="1"/>
-    <col min="20" max="20" width="16.125" customWidth="1"/>
+    <col min="5" max="6" width="13.625" customWidth="1"/>
+    <col min="7" max="7" width="13.125" customWidth="1"/>
+    <col min="8" max="8" width="10.25" customWidth="1"/>
+    <col min="9" max="9" width="10.125" customWidth="1"/>
+    <col min="10" max="10" width="13.625" customWidth="1"/>
+    <col min="17" max="17" width="14.5" customWidth="1"/>
+    <col min="18" max="18" width="14.875" customWidth="1"/>
+    <col min="19" max="19" width="15.75" customWidth="1"/>
+    <col min="20" max="20" width="14.5" customWidth="1"/>
+    <col min="21" max="21" width="16.125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:22" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:23" x14ac:dyDescent="0.15">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -472,54 +479,57 @@
         <v>1</v>
       </c>
       <c r="F1" t="s">
+        <v>22</v>
+      </c>
+      <c r="G1" t="s">
         <v>12</v>
       </c>
-      <c r="G1" t="s">
+      <c r="H1" t="s">
         <v>2</v>
       </c>
-      <c r="H1" t="s">
+      <c r="I1" t="s">
         <v>3</v>
       </c>
-      <c r="I1" t="s">
+      <c r="J1" t="s">
         <v>4</v>
       </c>
-      <c r="J1" t="s">
+      <c r="K1" t="s">
         <v>5</v>
       </c>
-      <c r="K1" t="s">
+      <c r="L1" t="s">
         <v>6</v>
       </c>
-      <c r="L1" t="s">
+      <c r="M1" t="s">
         <v>18</v>
       </c>
-      <c r="M1" t="s">
+      <c r="N1" t="s">
         <v>7</v>
       </c>
-      <c r="N1" t="s">
+      <c r="O1" t="s">
         <v>8</v>
       </c>
-      <c r="O1" t="s">
+      <c r="P1" t="s">
         <v>9</v>
       </c>
-      <c r="P1" t="s">
+      <c r="Q1" t="s">
         <v>13</v>
       </c>
-      <c r="Q1" t="s">
+      <c r="R1" t="s">
         <v>14</v>
       </c>
-      <c r="R1" t="s">
+      <c r="S1" t="s">
         <v>15</v>
       </c>
-      <c r="S1" t="s">
+      <c r="T1" t="s">
         <v>16</v>
       </c>
-      <c r="T1" t="s">
+      <c r="U1" t="s">
         <v>17</v>
       </c>
-      <c r="U1" t="s">
+      <c r="V1" t="s">
         <v>10</v>
       </c>
-      <c r="V1" t="s">
+      <c r="W1" t="s">
         <v>21</v>
       </c>
     </row>
